--- a/erp-server/erp-server-tms/src/main/resources/excel/transferLogisticsSupplier.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferLogisticsSupplier.xlsx
@@ -56,7 +56,7 @@
     <t>{.name}</t>
   </si>
   <si>
-    <t>{authStatusName</t>
+    <t>{.authStatusName</t>
   </si>
   <si>
     <t>{.disabledName}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferLogisticsSupplier.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferLogisticsSupplier.xlsx
@@ -56,7 +56,7 @@
     <t>{.name}</t>
   </si>
   <si>
-    <t>{.authStatusName</t>
+    <t>{.authStatusName}</t>
   </si>
   <si>
     <t>{.disabledName}</t>
